--- a/SistemaDinamicoDados/AmostrasFiltradas/KrigingVsg-/content/KrigingMetrics.xlsx
+++ b/SistemaDinamicoDados/AmostrasFiltradas/KrigingVsg-/content/KrigingMetrics.xlsx
@@ -477,28 +477,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-77760.03073540756</v>
+        <v>0.9999999999944761</v>
       </c>
       <c r="B2" t="n">
-        <v>9910.150855704427</v>
+        <v>1.33015501633583e-12</v>
       </c>
       <c r="C2" t="n">
-        <v>3809.997029413696</v>
+        <v>5.24968619910116e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>99.54974061093493</v>
+        <v>1.153323465613975e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>-6403522001499.759</v>
+        <v>0.9562145061421135</v>
       </c>
       <c r="F2" t="n">
-        <v>194627148887.1103</v>
+        <v>0.007209707809123286</v>
       </c>
       <c r="G2" t="n">
-        <v>580703.1373720907</v>
+        <v>0.4328304165045227</v>
       </c>
       <c r="H2" t="n">
-        <v>441165.6705673168</v>
+        <v>0.08490999828714688</v>
       </c>
     </row>
   </sheetData>
@@ -562,25 +562,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1.013684905815971e-24</v>
+        <v>4.657007329572078e-24</v>
       </c>
       <c r="C2" t="n">
-        <v>2.29657785575986e-11</v>
+        <v>2.888924818137864e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.006819202149011e-12</v>
+        <v>2.158010039265823e-12</v>
       </c>
       <c r="E2" t="n">
-        <v>-19.15870635892218</v>
+        <v>0.9471538230893431</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6126990026691517</v>
+        <v>0.008701637478195245</v>
       </c>
       <c r="G2" t="n">
-        <v>1.220210955802188</v>
+        <v>0.3140771782025401</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7827509199414279</v>
+        <v>0.09328256792238969</v>
       </c>
     </row>
   </sheetData>
@@ -644,25 +644,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.91945726527507e-25</v>
+        <v>1.723603315107096e-24</v>
       </c>
       <c r="C2" t="n">
-        <v>3.550178503307458e-11</v>
+        <v>8.667394646025801e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>5.40320022327053e-13</v>
+        <v>1.312860737133644e-12</v>
       </c>
       <c r="E2" t="n">
-        <v>-20.80721559576885</v>
+        <v>0.9248304425049965</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6628034065591264</v>
+        <v>0.01237739940627514</v>
       </c>
       <c r="G2" t="n">
-        <v>1.323490587502873</v>
+        <v>0.3783021060957873</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8141273896382104</v>
+        <v>0.1112537613129333</v>
       </c>
     </row>
   </sheetData>
@@ -726,25 +726,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3.378214885967948e-22</v>
+        <v>6.908682733776509e-28</v>
       </c>
       <c r="C2" t="n">
-        <v>1.174477724858709e-09</v>
+        <v>3.034793095680238e-13</v>
       </c>
       <c r="D2" t="n">
-        <v>1.837992079952454e-11</v>
+        <v>2.628437317832881e-14</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.826267970548727</v>
+        <v>0.9211324438127059</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1162946931097353</v>
+        <v>0.01298631089044089</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5245341015739891</v>
+        <v>0.4164950172273612</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3410200772824604</v>
+        <v>0.1139574959817953</v>
       </c>
     </row>
   </sheetData>
@@ -808,25 +808,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1.141493107824444e-24</v>
+        <v>1.218305748375661e-26</v>
       </c>
       <c r="C2" t="n">
-        <v>6.122106977049303e-11</v>
+        <v>4.932345609794374e-12</v>
       </c>
       <c r="D2" t="n">
-        <v>1.068406808207644e-12</v>
+        <v>1.103768883587348e-13</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.034572862422594</v>
+        <v>-0.05327331965044491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2442009269855826</v>
+        <v>0.1734317055432103</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7760733592507627</v>
+        <v>3.317871088273187</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4941669019527538</v>
+        <v>0.4164513243384037</v>
       </c>
     </row>
   </sheetData>
@@ -890,25 +890,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.338037732099748e-25</v>
+        <v>1.17034938419928e-24</v>
       </c>
       <c r="C2" t="n">
-        <v>2.772200565709146e-11</v>
+        <v>4.715015097297313e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>4.835325978773042e-13</v>
+        <v>1.081826873487288e-12</v>
       </c>
       <c r="E2" t="n">
-        <v>-28.34528638580174</v>
+        <v>0.9289517906827123</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8919137657691781</v>
+        <v>0.01169877930808841</v>
       </c>
       <c r="G2" t="n">
-        <v>1.585673140932931</v>
+        <v>0.4389349894688756</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9444118623615325</v>
+        <v>0.1081608954663764</v>
       </c>
     </row>
   </sheetData>
